--- a/scripts/tests/fixtures/overview/workbook-sync-run-changes.xlsx
+++ b/scripts/tests/fixtures/overview/workbook-sync-run-changes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
   <si>
     <t>{{report.title}}</t>
   </si>
@@ -39,51 +39,54 @@
     <t>Source</t>
   </si>
   <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>{{table:run_errors|source,about,code,detail}}</t>
+  </si>
+  <si>
+    <t>Portfolio</t>
+  </si>
+  <si>
+    <t>Portfolio name</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Trade date</t>
+  </si>
+  <si>
+    <t>Leg</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>ISIN</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
     <t>Batch</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Detail</t>
-  </si>
-  <si>
-    <t>{{table:run_errors|source,batch_id,code,detail}}</t>
-  </si>
-  <si>
-    <t>Portfolio</t>
-  </si>
-  <si>
-    <t>Portfolio name</t>
-  </si>
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Trade date</t>
-  </si>
-  <si>
-    <t>Leg</t>
-  </si>
-  <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>ISIN</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Outcome</t>
-  </si>
-  <si>
     <t>Row</t>
   </si>
   <si>
@@ -162,13 +165,13 @@
     <t>Proposals</t>
   </si>
   <si>
-    <t>604</t>
+    <t>610</t>
   </si>
   <si>
     <t>Batches by state</t>
   </si>
   <si>
-    <t>committed 3</t>
+    <t>committed 4</t>
   </si>
   <si>
     <t>Loop</t>
@@ -192,7 +195,7 @@
     <t>Connector state</t>
   </si>
   <si>
-    <t>finished</t>
+    <t>DONE_WITH_ERRORS</t>
   </si>
   <si>
     <t>Check verdict</t>
@@ -216,24 +219,27 @@
     <t>Batches read</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Batches not read (rejected, abandoned, pending)</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Batches previewed for this file</t>
+  </si>
+  <si>
+    <t>Batches committed with counts only</t>
+  </si>
+  <si>
+    <t>Movements changed</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>Batches not read (rejected, abandoned, pending)</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Batches previewed for this file</t>
-  </si>
-  <si>
-    <t>Batches committed with counts only</t>
-  </si>
-  <si>
-    <t>Movements changed</t>
-  </si>
-  <si>
     <t>Portfolios</t>
   </si>
   <si>
@@ -249,12 +255,39 @@
     <t>Rows unchanged</t>
   </si>
   <si>
-    <t>540</t>
+    <t>542</t>
   </si>
   <si>
     <t>Rows refused</t>
   </si>
   <si>
+    <t>Rows changed in targets this file does not list</t>
+  </si>
+  <si>
+    <t>Rows changed that no portfolio could be named for</t>
+  </si>
+  <si>
+    <t>connector</t>
+  </si>
+  <si>
+    <t>contract 200900003 · valuationHistoryByContract</t>
+  </si>
+  <si>
+    <t>TIMEOUT</t>
+  </si>
+  <si>
+    <t>DistrInfo did not answer within 30 s</t>
+  </si>
+  <si>
+    <t>conseq/hartland/run-20260930-0530/getContractInfo.200900002.csv · investment.position · getContractInfo</t>
+  </si>
+  <si>
+    <t>BATCH_REJECTED</t>
+  </si>
+  <si>
+    <t>the door rejected this batch</t>
+  </si>
+  <si>
     <t>conseq:200900001</t>
   </si>
   <si>
@@ -330,16 +363,19 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-10-01T08:00:00Z</t>
+    <t>2026-10-04T10:30:21Z</t>
   </si>
   <si>
     <t>Changes: would — nothing is committed yet; these are what committing would change; did — committed; these are what changed; mixed — some batches committed, some still held.</t>
   </si>
   <si>
-    <t>Only rows that change something are listed; 540 unchanged rows are counted, not listed.</t>
+    <t>Only rows that change something are listed; 542 unchanged rows are counted, not listed.</t>
   </si>
   <si>
     <t>Read from studio-bff's change projection (IA-C20) with the caller's own bearer: committed batches from their entry records, held and failed ones from their kept preview or a fresh one.</t>
+  </si>
+  <si>
+    <t>4 changed row(s) belong to targets this file does not list — the provider's valuation points (investment.portfolio_valuation) among them: they are counted on the Run sheet ("Rows changed in targets this file does not list"), not listed.</t>
   </si>
 </sst>
 </file>
@@ -430,23 +466,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="34.0"/>
-    <col min="2" max="2" customWidth="true" width="20.0"/>
+    <col min="2" max="2" customWidth="true" width="34.0"/>
     <col min="3" max="3" customWidth="true" width="14.0"/>
     <col min="4" max="4" customWidth="true" width="34.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -459,204 +495,242 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s" s="3">
+      <c r="A28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="s" s="5">
+    <row r="31">
+      <c r="A31" t="s" s="5">
         <v>6</v>
       </c>
-      <c r="B29" t="s" s="5">
+      <c r="B31" t="s" s="5">
         <v>7</v>
       </c>
-      <c r="C29" t="s" s="5">
+      <c r="C31" t="s" s="5">
         <v>8</v>
       </c>
-      <c r="D29" t="s" s="5">
+      <c r="D31" t="s" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -685,12 +759,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -728,33 +802,33 @@
         <v>21</v>
       </c>
       <c r="L4" t="s" s="5">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="M4" t="s" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>46294.0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>10.0</v>
@@ -763,13 +837,13 @@
         <v>1234.5</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>0.0</v>
@@ -777,38 +851,38 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>46294.0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="H6" s="10"/>
       <c r="I6" s="9" t="n">
         <v>1234.5</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>1.0</v>
@@ -816,38 +890,38 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>46293.0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="9" t="n">
         <v>500.0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>4.0</v>
@@ -875,12 +949,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -894,30 +968,30 @@
         <v>13</v>
       </c>
       <c r="D4" t="s" s="6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s" s="6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" t="s" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D5" s="12" t="n">
         <v>2.0</v>
@@ -937,13 +1011,13 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>1.0</v>
@@ -978,23 +1052,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s" s="6">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -1015,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="30.0"/>
@@ -1024,12 +1098,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -1042,62 +1116,67 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>107</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
